--- a/data/trans_camb/P14B23-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Edad-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,74</t>
+          <t>-0,19; 1,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,83</t>
+          <t>0,46; 6,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,03</t>
+          <t>0,38; 4,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,66</t>
+          <t>0,98; 7,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,16</t>
+          <t>0,31; 2,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,9</t>
+          <t>1,13; 5,07</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,85; —</t>
+          <t>-23,42; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,24; —</t>
+          <t>-9,87; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1816,22</t>
+          <t>2,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>122,07; 4185,95</t>
+          <t>128,17; 4606,59</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,37</t>
+          <t>-1,21; 0,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,4</t>
+          <t>-0,78; 1,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,3</t>
+          <t>-3,42; -0,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,64</t>
+          <t>-1,14; 3,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; -0,13</t>
+          <t>-1,95; -0,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,38</t>
+          <t>-0,32; 2,35</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 260,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-94,17; 458,46</t>
+          <t>-90,45; 484,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,65; -3,51</t>
+          <t>-87,82; 7,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 182,92</t>
+          <t>-31,69; 193,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,62; -5,87</t>
+          <t>-84,96; -9,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 189,2</t>
+          <t>-19,26; 191,34</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -0,18</t>
+          <t>-4,04; -0,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,13</t>
+          <t>-1,53; 3,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,75</t>
+          <t>-5,19; -0,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,31</t>
+          <t>-4,78; 0,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,98</t>
+          <t>-3,91; -0,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,92</t>
+          <t>-2,43; 1,01</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,81; -3,3</t>
+          <t>-81,2; -5,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 124,8</t>
+          <t>-34,19; 123,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,03; -11,29</t>
+          <t>-63,77; -6,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 6,92</t>
+          <t>-58,42; 4,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,72; -20,5</t>
+          <t>-63,07; -18,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 22,44</t>
+          <t>-40,34; 23,81</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,44</t>
+          <t>-1,53; 2,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,5</t>
+          <t>-2,07; 3,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,9</t>
+          <t>-2,92; 3,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,77</t>
+          <t>-2,78; 2,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,23</t>
+          <t>-1,68; 1,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,46</t>
+          <t>-2,17; 2,46</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 171,37</t>
+          <t>-43,77; 131,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 191,58</t>
+          <t>-46,13; 189,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 45,66</t>
+          <t>-32,05; 53,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 47,44</t>
+          <t>-27,57; 48,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 51,09</t>
+          <t>-26,88; 45,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 55,65</t>
+          <t>-33,1; 55,59</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,85</t>
+          <t>-3,04; 2,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,9</t>
+          <t>-1,39; 3,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 2,52</t>
+          <t>-6,27; 2,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 2,03</t>
+          <t>-5,44; 1,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,28</t>
+          <t>-3,87; 1,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,99</t>
+          <t>-2,63; 2,11</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 71,38</t>
+          <t>-53,53; 89,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 136,38</t>
+          <t>-24,96; 138,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 24,92</t>
+          <t>-39,68; 19,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 21,69</t>
+          <t>-34,13; 16,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 15,86</t>
+          <t>-37,35; 19,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 26,97</t>
+          <t>-25,14; 27,71</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,49; -0,25</t>
+          <t>-5,58; -0,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,85</t>
+          <t>-3,9; 1,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 1,24</t>
+          <t>-8,45; 1,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -2,9</t>
+          <t>-15,49; -3,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -0,09</t>
+          <t>-5,97; -0,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -1,57</t>
+          <t>-8,2; -1,21</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-95,04; -2,72</t>
+          <t>-93,84; -1,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 101,09</t>
+          <t>-65,85; 86,37</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 11,04</t>
+          <t>-47,34; 13,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-83,67; -22,93</t>
+          <t>-82,18; -21,38</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 0,06</t>
+          <t>-53,44; -0,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,67; -19,85</t>
+          <t>-71,94; -17,06</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,99</t>
+          <t>-3,94; 2,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 4,41</t>
+          <t>-2,46; 4,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 1,43</t>
+          <t>-9,18; 1,36</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,21</t>
+          <t>-8,88; -0,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,25</t>
+          <t>-5,81; 1,37</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 0,64</t>
+          <t>-5,53; 0,74</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-59,74; 161,53</t>
+          <t>-63,52; 148,74</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-46,41; 215,2</t>
+          <t>-44,71; 212,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 12,8</t>
+          <t>-51,15; 11,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,59; -1,17</t>
+          <t>-47,5; -0,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 13,44</t>
+          <t>-46,66; 15,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 9,11</t>
+          <t>-42,15; 8,78</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,25</t>
+          <t>-1,23; 0,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,1</t>
+          <t>0,14; 2,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,05</t>
+          <t>-2,66; -0,08</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,45</t>
+          <t>-2,43; 0,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,15</t>
+          <t>-1,74; -0,25</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,0</t>
+          <t>-0,68; 1,07</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 13,37</t>
+          <t>-43,33; 13,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3,49; 99,1</t>
+          <t>4,66; 95,98</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,62; -0,58</t>
+          <t>-30,63; -1,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 6,4</t>
+          <t>-28,27; 5,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -3,12</t>
+          <t>-30,04; -4,63</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 20,39</t>
+          <t>-11,83; 21,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P14B23-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Edad-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,01</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>2,47</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,8</t>
+          <t>-0,18; 1,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,67</t>
+          <t>0,4; 4,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,21</t>
+          <t>0,52; 4,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,71</t>
+          <t>0,98; 6,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,28</t>
+          <t>0,31; 2,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,07</t>
+          <t>1,08; 4,55</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1115,19%</t>
+          <t>1070,98%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>755,84%</t>
+          <t>670,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>834,48%</t>
+          <t>780,42%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,42; —</t>
+          <t>-20,64; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,87; —</t>
+          <t>-2,16; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,0; —</t>
+          <t>-12,05; 2814,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>128,17; 4606,59</t>
+          <t>115,96; 3651,63</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>1,33</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,35</t>
+          <t>-1,11; 0,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,43</t>
+          <t>-0,34; 2,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -0,19</t>
+          <t>-3,51; -0,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,77</t>
+          <t>-0,38; 4,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; -0,23</t>
+          <t>-1,92; -0,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,35</t>
+          <t>0,03; 2,83</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>109,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 260,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 484,61</t>
+          <t>-49,56; 1064,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,82; 7,19</t>
+          <t>-88,45; 9,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 193,5</t>
+          <t>-14,26; 236,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,96; -9,41</t>
+          <t>-84,22; -1,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 191,34</t>
+          <t>-5,46; 239,66</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,33</t>
+          <t>-3,98; -0,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,19</t>
+          <t>-1,96; 2,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; -0,51</t>
+          <t>-5,16; -0,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,18</t>
+          <t>-4,15; 0,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; -0,87</t>
+          <t>-4,05; -0,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,01</t>
+          <t>-2,32; 1,14</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-32,05%</t>
+          <t>-20,83%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,57%</t>
+          <t>-11,77%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-81,2; -5,55</t>
+          <t>-79,72; 0,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 123,54</t>
+          <t>-42,67; 109,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,77; -6,32</t>
+          <t>-62,23; -9,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 4,05</t>
+          <t>-49,36; 17,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,07; -18,28</t>
+          <t>-64,88; -17,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 23,81</t>
+          <t>-37,73; 31,01</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,29</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,29</t>
+          <t>-1,37; 2,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 3,44</t>
+          <t>0,21; 4,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,2</t>
+          <t>-3,0; 3,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,88</t>
+          <t>-2,15; 3,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,99</t>
+          <t>-1,54; 2,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,46</t>
+          <t>-0,21; 3,37</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 131,43</t>
+          <t>-43,16; 145,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 189,45</t>
+          <t>-1,86; 270,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 53,7</t>
+          <t>-31,67; 53,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 48,33</t>
+          <t>-23,69; 49,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 45,9</t>
+          <t>-25,28; 48,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 55,59</t>
+          <t>-5,3; 85,83</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,27</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,3</t>
+          <t>-3,32; 2,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,96</t>
+          <t>-1,56; 3,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,19</t>
+          <t>-6,36; 2,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 1,8</t>
+          <t>-5,53; 1,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,46</t>
+          <t>-3,91; 1,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,11</t>
+          <t>-2,9; 1,98</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-12,14%</t>
+          <t>-11,42%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-2,38%</t>
+          <t>-2,98%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 89,92</t>
+          <t>-56,56; 75,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 138,6</t>
+          <t>-26,68; 129,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,68; 19,17</t>
+          <t>-40,82; 21,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 16,07</t>
+          <t>-33,62; 18,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 19,82</t>
+          <t>-37,99; 18,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 27,71</t>
+          <t>-27,02; 26,21</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-8,12</t>
+          <t>-4,61</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,3</t>
+          <t>-2,96</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -0,45</t>
+          <t>-5,84; -0,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,56</t>
+          <t>-4,55; 1,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,52</t>
+          <t>-8,53; 1,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -3,02</t>
+          <t>-8,83; -0,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,97; -0,03</t>
+          <t>-5,87; 0,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -1,21</t>
+          <t>-5,61; -0,41</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-17,39%</t>
+          <t>-22,3%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-54,43%</t>
+          <t>-30,92%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-44,43%</t>
+          <t>-30,57%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-93,84; -1,83</t>
+          <t>-93,54; 1,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-65,85; 86,37</t>
+          <t>-69,94; 68,0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 13,04</t>
+          <t>-47,05; 15,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-82,18; -21,38</t>
+          <t>-50,29; -1,68</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-53,44; -0,21</t>
+          <t>-52,8; 3,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-71,94; -17,06</t>
+          <t>-48,98; -4,71</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>-4,22</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-2,05</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,91</t>
+          <t>-3,45; 3,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 4,22</t>
+          <t>-2,52; 4,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 1,36</t>
+          <t>-8,76; 2,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -0,27</t>
+          <t>-8,6; -0,01</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 1,37</t>
+          <t>-5,43; 1,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,74</t>
+          <t>-4,87; 1,25</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-28,73%</t>
+          <t>-27,63%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-20,74%</t>
+          <t>-19,01%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 148,74</t>
+          <t>-60,96; 176,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 212,84</t>
+          <t>-45,17; 241,78</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-51,15; 11,45</t>
+          <t>-49,14; 19,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,5; -0,67</t>
+          <t>-46,8; 0,03</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 15,49</t>
+          <t>-43,43; 14,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,15; 8,78</t>
+          <t>-38,27; 14,87</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,29</t>
+          <t>-1,39; 0,18</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,1</t>
+          <t>0,46; 2,19</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,08</t>
+          <t>-2,63; -0,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,39</t>
+          <t>-1,31; 1,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; -0,25</t>
+          <t>-1,6; -0,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,07</t>
+          <t>-0,12; 1,39</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-10,01%</t>
+          <t>-0,31%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 13,85</t>
+          <t>-45,85; 9,1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4,66; 95,98</t>
+          <t>16,14; 106,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -1,05</t>
+          <t>-30,25; -0,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 5,49</t>
+          <t>-15,2; 16,85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-30,04; -4,63</t>
+          <t>-28,7; -4,15</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 21,51</t>
+          <t>-2,14; 28,15</t>
         </is>
       </c>
     </row>
